--- a/processed_ruby_restored_xlsx/sc202_共有２：天体観測ルート分岐前.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc202_共有２：天体観測ルート分岐前.ss.xlsx
@@ -577,8 +577,8 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>The students also answered cheerfully and quickly took
-their seats.</t>
+          <t>The students also answered cheerfully and quickly
+took their seats.</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -901,9 +901,9 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>When I raised my hand energetically to ask a question,
-Nono-chan rode my momentum with her own energy and
-said.</t>
+          <t>When I raised my hand energetically to ask a
+question, Nono-chan rode my momentum with her own
+energy and said.</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1070,9 +1070,9 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>It's something we could do anytime, but giving it some
-kind of special feeling suddenly makes it so much more
-fun.</t>
+          <t>It's something we could do anytime, but giving it
+some kind of special feeling suddenly makes it so
+much more fun.</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1791,8 +1791,8 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>I’ll need to do meal prep, bring the futon in, and get
-a bunch of other things ready….</t>
+          <t>I’ll need to do meal prep, bring the futon in, and
+get a bunch of other things ready….</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1905,8 +1905,8 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>Everyone hates the smell of wax when they're trying to
-sleep, right?</t>
+          <t>Everyone hates the smell of wax when they're trying
+to sleep, right?</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2077,8 +2077,8 @@
       <c r="B105" s="1" t="inlineStr">
         <is>
           <t>I was grinning to myself when the chime rang and
-Nono-chan, having finished her classes, came by to see
-how things were.</t>
+Nono-chan, having finished her classes, came by to
+see how things were.</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2138,8 +2138,8 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ With this, no one will get mad if I flop down on
-the floor！」</t>
+          <t>「Yes！ With this, no one will get mad if I flop down
+on the floor！」</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2615,8 +2615,8 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, who arrived last of all, smiled as she
-watched Nono-chan flopping on the floor.</t>
+          <t>Rurichiyo-chan, who arrived last of all, smiled as
+she watched Nono-chan flopping on the floor.</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2661,8 +2661,8 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>Even Rurichiyo-chan, acting unlike her usual self, lay
-down and started rolling around on the floor.</t>
+          <t>Even Rurichiyo-chan, acting unlike her usual self,
+lay down and started rolling around on the floor.</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2753,8 +2753,8 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Seeing Rurichiyo-chan, Miru-chan and Rin-chan also lay
-down and began rolling around.</t>
+          <t>Seeing Rurichiyo-chan, Miru-chan and Rin-chan also
+lay down and began rolling around.</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2997,8 +2997,8 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>「Fuwa！？ Y-yeah！ Everyone, stop lazing around and let's
-go back to the classroom！」</t>
+          <t>「Fuwa！？ Y-yeah！ Everyone, stop lazing around and
+let's go back to the classroom！」</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3044,8 +3044,8 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>「That's right. Let's save the lazing-around for later,
-shall we？」</t>
+          <t>「That's right. Let's save the lazing-around for
+later, shall we？」</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3090,8 +3090,8 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>When Nono stood up, everyone imitated her and stood up
-too.</t>
+          <t>When Nono stood up, everyone imitated her and stood
+up too.</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3106,8 +3106,8 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>And as we were heading back to the classroom, Rin-chan
-glanced back at me.</t>
+          <t>And as we were heading back to the classroom,
+Rin-chan glanced back at me.</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3335,9 +3335,9 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>When I suddenly realized it, Rin-chan, who should have
-gone back to the classroom, was peeking from behind
-the door.</t>
+          <t>When I suddenly realized it, Rin-chan, who should
+have gone back to the classroom, was peeking from
+behind the door.</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3429,9 +3429,9 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Dinner and a late-night snack, and if it comes to it I
-might as well cook breakfast and lunch for tomorrow as
-well.</t>
+          <t>Dinner and a late-night snack, and if it comes to it
+I might as well cook breakfast and lunch for tomorrow
+as well.</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3478,9 +3478,9 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>Just the thought of being able to lounge around in the
-assembly hall gets Nono-chan and even Rurichiyo-chan
-all worked up.</t>
+          <t>Just the thought of being able to lounge around in
+the assembly hall gets Nono-chan and even
+Rurichiyo-chan all worked up.</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3649,8 +3649,8 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>If everyone's staying overnight in the same room, this
-sort of thing is, if anything, to be expected.</t>
+          <t>If everyone's staying overnight in the same room,
+this sort of thing is, if anything, to be expected.</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3926,8 +3926,8 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, staring at her own pillow, for reasons
-unknown tossed the pillow at Nono-chan.</t>
+          <t>Rurichiyo-chan, staring at her own pillow, for
+reasons unknown tossed the pillow at Nono-chan.</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -4018,8 +4018,8 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>...Nono-chan picked up the pillow that had been thrown
-and, giddily, hurled it at Rurichiyo-chan.</t>
+          <t>...Nono-chan picked up the pillow that had been
+thrown and, giddily, hurled it at Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4263,8 +4263,8 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>At that point, everyone got so tired from playing that
-they fell asleep.</t>
+          <t>At that point, everyone got so tired from playing
+that they fell asleep.</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4279,8 +4279,8 @@
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>Seeing how they’d been running around so energetically
-just a bit ago, can you blame them？</t>
+          <t>Seeing how they’d been running around so
+energetically just a bit ago, can you blame them？</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4312,8 +4312,8 @@
       <c r="B250" s="1" t="inlineStr">
         <is>
           <t>Saying you’d take a short nap until the scheduled
-time—and then actually falling asleep—is so typical of
-little kids.</t>
+time—and then actually falling asleep—is so typical
+of little kids.</t>
         </is>
       </c>
       <c r="C250" t="n">

--- a/processed_ruby_restored_xlsx/sc202_共有２：天体観測ルート分岐前.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc202_共有２：天体観測ルート分岐前.ss.xlsx
@@ -639,8 +639,8 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>「Okaay... So then, without further ado, I’m going to
-announce today’s special lesson！」</t>
+          <t>Okaay... So then, without further ado, I’m going to
+announce today’s special lesson！</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -855,7 +855,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>「Sensei！ What is this special lesson！？」</t>
+          <t>Sensei！ What is this special lesson！？</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1102,8 +1102,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>「…So that's the situation, Janitor-sensei — is that
-alright？」</t>
+          <t>…So that's the situation, Janitor-sensei — is that
+alright？</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2476,8 +2476,8 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>「Both of you！ Janitor-sensei went to the trouble of
-cleaning this up for us, so don't make it dirty！」</t>
+          <t>Both of you！ Janitor-sensei went to the trouble of
+cleaning this up for us, so don't make it dirty！</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>「Hmm...?！」</t>
+          <t>「Hmm...?！</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Yeah... but lazing around, huh...?</t>
+          <t>Yeah... but lazing around, huh...?"</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>「Here I go~！ There~！」</t>
+          <t>Here I go~！ There~！</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>「Geez... you all are getting way too excited！」</t>
+          <t>Geez... you all are getting way too excited！</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu！ You got me...！」</t>
+          <t>Ufufu！ You got me...！</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>「Uwahp！ Phew... Rin, you're pretty good...！」</t>
+          <t>Uwahp！ Phew... Rin, you」re pretty good...！</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>「Fufu, fu... MiruMiru, you too...」</t>
+          <t>Fufu, fu... MiruMiru, you too...</t>
         </is>
       </c>
       <c r="C239" t="n">
